--- a/SpreadSheet/SayingSS.xlsx
+++ b/SpreadSheet/SayingSS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="saying" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="saying" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">saying!$A$1:$V$1003</definedName>
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="623">
   <si>
     <t>saying</t>
   </si>
@@ -2060,6 +2060,139 @@
   </si>
   <si>
     <t>抑圧は宗教を繁栄させるだけだ</t>
+  </si>
+  <si>
+    <t>俺は俺のことを好きな人が好きだ</t>
+  </si>
+  <si>
+    <t>映画「チェーンソーマン レゼ篇」</t>
+  </si>
+  <si>
+    <t>私も十本に一本くらいしか面白い映画には出会えないよ
+でもその一本に人生を変えられた事があるんだ</t>
+  </si>
+  <si>
+    <t>それは弱さじゃない
+強さの種よ</t>
+  </si>
+  <si>
+    <t>アニメ「地獄楽」</t>
+  </si>
+  <si>
+    <t>自分に嘘をつき続けてきた僕には、
+他人にしか嘘をつかない彼女の姿が、自分で眩しくて･･･
+胸が詰まるほど羨ましいんだ</t>
+  </si>
+  <si>
+    <t>すぐに全てを理解しようとすれば、欲求不満に陥るだけだ
+まずは受け入れる</t>
+  </si>
+  <si>
+    <t>ノーベル物理学賞 ミシェル・デボレ</t>
+  </si>
+  <si>
+    <t>努力は運の幅を広げてくれる</t>
+  </si>
+  <si>
+    <t>マンガ「ブルーピリオド」</t>
+  </si>
+  <si>
+    <t>トライ＆エラー
+トライ＆エラー
+トライ＆エラーよ！</t>
+  </si>
+  <si>
+    <t>好きなことをやるって
+いつでも楽しいって意味じゃないよ</t>
+  </si>
+  <si>
+    <t>他人（ひと）の世界をうらやんでいても仕方ない
+自分の世界は自分で変えなければ</t>
+  </si>
+  <si>
+    <t>マンガ「のだめカンタービレ」</t>
+  </si>
+  <si>
+    <t>負けたことは忘れていいんです
+次勝てばいい!!</t>
+  </si>
+  <si>
+    <t>マンガ「重版出来！」</t>
+  </si>
+  <si>
+    <t>何も捨てることができない人には
+何も変えることはできない</t>
+  </si>
+  <si>
+    <t>マンガ「進撃の巨人」</t>
+  </si>
+  <si>
+    <t>誰しも人間、理想を求めるが、常に理想ではいられない</t>
+  </si>
+  <si>
+    <t>映画「教皇選挙」</t>
+  </si>
+  <si>
+    <t>自分たちは理想を追うただの人間であって、理想そのものではない</t>
+  </si>
+  <si>
+    <t>もし確信しかなく疑いが何もなければ、謎は何もなくなるだろう
+したがって信仰も必要なくなる</t>
+  </si>
+  <si>
+    <t>戦うとおっしゃるが、何と戦うのです？</t>
+  </si>
+  <si>
+    <t>想いってのは言葉にしないと伝わらないんだぜ</t>
+  </si>
+  <si>
+    <t>アニメ「葬送のフリーレン」</t>
+  </si>
+  <si>
+    <t>必死に生きてきた人の行きつく先が無であっていいはずがありません</t>
+  </si>
+  <si>
+    <t>生きているということは誰かに知ってもらって覚えていてもらうことだ
+ほんの少しでいい
+誰かの人生を変えてあげればいい
+きっとそれだけで十分なんだ</t>
+  </si>
+  <si>
+    <t>僕達が求めているのは誰かを助けることであって感謝の言葉じゃない
+相手に貸しを作ってしまったら本当の意味で助けたことにはならないだろう</t>
+  </si>
+  <si>
+    <t>理想の大人を目指して大人の振りをしてそれを積み重ねてきただけです</t>
+  </si>
+  <si>
+    <t>必要なものは覚悟だけだったのです
+必死に積み上げてきたものは決して裏切りません</t>
+  </si>
+  <si>
+    <t>魔法は探し求めている時が一番楽しいんだよ</t>
+  </si>
+  <si>
+    <t>「いつか」なんて時は私たちの人生には存在しない</t>
+  </si>
+  <si>
+    <t>親ってのは無条件の愛で自分に尽くしてくれる人のことだよ</t>
+  </si>
+  <si>
+    <t>アニメ「不滅のあなたへ」</t>
+  </si>
+  <si>
+    <t>自分の生き方は与えられるものじゃない
+自分で勝ち取るんだ</t>
+  </si>
+  <si>
+    <t>問題では無いと思っているところが問題なのでは？</t>
+  </si>
+  <si>
+    <t>人間、命の使いどころというものがある気がする
+もしも命が無限なら生きることにどんな意味を見出せばいいんだ？</t>
+  </si>
+  <si>
+    <t>求める人のために尽くし、弱きものを助けろ</t>
   </si>
 </sst>
 </file>
@@ -2163,6 +2296,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12766,7 +12903,9 @@
       <c r="B350" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C350" s="2"/>
+      <c r="C350" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="D350" s="2"/>
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
@@ -12794,7 +12933,9 @@
       <c r="B351" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C351" s="2"/>
+      <c r="C351" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="D351" s="2"/>
       <c r="E351" s="2"/>
       <c r="F351" s="2"/>
@@ -12822,7 +12963,9 @@
       <c r="B352" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="C352" s="2"/>
+      <c r="C352" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="D352" s="2"/>
       <c r="E352" s="2"/>
       <c r="F352" s="2"/>
@@ -12850,7 +12993,9 @@
       <c r="B353" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="C353" s="2"/>
+      <c r="C353" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="D353" s="2"/>
       <c r="E353" s="2"/>
       <c r="F353" s="2"/>
@@ -12906,7 +13051,9 @@
       <c r="B355" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="C355" s="2"/>
+      <c r="C355" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="D355" s="2"/>
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
@@ -13074,7 +13221,9 @@
       <c r="B361" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="C361" s="2"/>
+      <c r="C361" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="D361" s="2"/>
       <c r="E361" s="2"/>
       <c r="F361" s="2"/>
@@ -13130,7 +13279,9 @@
       <c r="B363" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="C363" s="2"/>
+      <c r="C363" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="D363" s="2"/>
       <c r="E363" s="2"/>
       <c r="F363" s="2"/>
@@ -13158,7 +13309,9 @@
       <c r="B364" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="C364" s="2"/>
+      <c r="C364" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="D364" s="2"/>
       <c r="E364" s="2"/>
       <c r="F364" s="2"/>
@@ -13186,7 +13339,9 @@
       <c r="B365" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="C365" s="2"/>
+      <c r="C365" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="D365" s="2"/>
       <c r="E365" s="2"/>
       <c r="F365" s="2"/>
@@ -13236,8 +13391,12 @@
       <c r="V366" s="2"/>
     </row>
     <row r="367">
-      <c r="A367" s="2"/>
-      <c r="B367" s="2"/>
+      <c r="A367" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="B367" s="5" t="s">
+        <v>586</v>
+      </c>
       <c r="C367" s="2"/>
       <c r="D367" s="2"/>
       <c r="E367" s="2"/>
@@ -13260,8 +13419,12 @@
       <c r="V367" s="2"/>
     </row>
     <row r="368">
-      <c r="A368" s="2"/>
-      <c r="B368" s="2"/>
+      <c r="A368" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="B368" s="5" t="s">
+        <v>586</v>
+      </c>
       <c r="C368" s="2"/>
       <c r="D368" s="2"/>
       <c r="E368" s="2"/>
@@ -13284,8 +13447,12 @@
       <c r="V368" s="2"/>
     </row>
     <row r="369">
-      <c r="A369" s="2"/>
-      <c r="B369" s="2"/>
+      <c r="A369" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="B369" s="5" t="s">
+        <v>589</v>
+      </c>
       <c r="C369" s="2"/>
       <c r="D369" s="2"/>
       <c r="E369" s="2"/>
@@ -13308,8 +13475,12 @@
       <c r="V369" s="2"/>
     </row>
     <row r="370">
-      <c r="A370" s="2"/>
-      <c r="B370" s="2"/>
+      <c r="A370" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="B370" s="5" t="s">
+        <v>589</v>
+      </c>
       <c r="C370" s="2"/>
       <c r="D370" s="2"/>
       <c r="E370" s="2"/>
@@ -13332,8 +13503,12 @@
       <c r="V370" s="2"/>
     </row>
     <row r="371">
-      <c r="A371" s="2"/>
-      <c r="B371" s="2"/>
+      <c r="A371" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>592</v>
+      </c>
       <c r="C371" s="2"/>
       <c r="D371" s="2"/>
       <c r="E371" s="2"/>
@@ -13356,9 +13531,15 @@
       <c r="V371" s="2"/>
     </row>
     <row r="372">
-      <c r="A372" s="2"/>
-      <c r="B372" s="2"/>
-      <c r="C372" s="2"/>
+      <c r="A372" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="B372" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="C372" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="D372" s="2"/>
       <c r="E372" s="2"/>
       <c r="F372" s="2"/>
@@ -13380,9 +13561,15 @@
       <c r="V372" s="2"/>
     </row>
     <row r="373">
-      <c r="A373" s="2"/>
-      <c r="B373" s="2"/>
-      <c r="C373" s="2"/>
+      <c r="A373" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="B373" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="C373" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="D373" s="2"/>
       <c r="E373" s="2"/>
       <c r="F373" s="2"/>
@@ -13404,9 +13591,15 @@
       <c r="V373" s="2"/>
     </row>
     <row r="374">
-      <c r="A374" s="2"/>
-      <c r="B374" s="2"/>
-      <c r="C374" s="2"/>
+      <c r="A374" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="C374" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="D374" s="2"/>
       <c r="E374" s="2"/>
       <c r="F374" s="2"/>
@@ -13428,9 +13621,15 @@
       <c r="V374" s="2"/>
     </row>
     <row r="375">
-      <c r="A375" s="2"/>
-      <c r="B375" s="2"/>
-      <c r="C375" s="2"/>
+      <c r="A375" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="C375" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="D375" s="2"/>
       <c r="E375" s="2"/>
       <c r="F375" s="2"/>
@@ -13452,9 +13651,15 @@
       <c r="V375" s="2"/>
     </row>
     <row r="376">
-      <c r="A376" s="2"/>
-      <c r="B376" s="2"/>
-      <c r="C376" s="2"/>
+      <c r="A376" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="B376" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="C376" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="D376" s="2"/>
       <c r="E376" s="2"/>
       <c r="F376" s="2"/>
@@ -13476,8 +13681,12 @@
       <c r="V376" s="2"/>
     </row>
     <row r="377">
-      <c r="A377" s="2"/>
-      <c r="B377" s="2"/>
+      <c r="A377" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="B377" s="5" t="s">
+        <v>602</v>
+      </c>
       <c r="C377" s="2"/>
       <c r="D377" s="2"/>
       <c r="E377" s="2"/>
@@ -13500,8 +13709,12 @@
       <c r="V377" s="2"/>
     </row>
     <row r="378">
-      <c r="A378" s="2"/>
-      <c r="B378" s="2"/>
+      <c r="A378" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="B378" s="5" t="s">
+        <v>604</v>
+      </c>
       <c r="C378" s="2"/>
       <c r="D378" s="2"/>
       <c r="E378" s="2"/>
@@ -13524,8 +13737,12 @@
       <c r="V378" s="2"/>
     </row>
     <row r="379">
-      <c r="A379" s="2"/>
-      <c r="B379" s="2"/>
+      <c r="A379" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="B379" s="5" t="s">
+        <v>604</v>
+      </c>
       <c r="C379" s="2"/>
       <c r="D379" s="2"/>
       <c r="E379" s="2"/>
@@ -13548,8 +13765,12 @@
       <c r="V379" s="2"/>
     </row>
     <row r="380">
-      <c r="A380" s="2"/>
-      <c r="B380" s="2"/>
+      <c r="A380" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="B380" s="5" t="s">
+        <v>604</v>
+      </c>
       <c r="C380" s="2"/>
       <c r="D380" s="2"/>
       <c r="E380" s="2"/>
@@ -13572,8 +13793,12 @@
       <c r="V380" s="2"/>
     </row>
     <row r="381">
-      <c r="A381" s="2"/>
-      <c r="B381" s="2"/>
+      <c r="A381" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="B381" s="5" t="s">
+        <v>604</v>
+      </c>
       <c r="C381" s="2"/>
       <c r="D381" s="2"/>
       <c r="E381" s="2"/>
@@ -13596,8 +13821,12 @@
       <c r="V381" s="2"/>
     </row>
     <row r="382">
-      <c r="A382" s="2"/>
-      <c r="B382" s="2"/>
+      <c r="A382" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="B382" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="C382" s="2"/>
       <c r="D382" s="2"/>
       <c r="E382" s="2"/>
@@ -13620,8 +13849,12 @@
       <c r="V382" s="2"/>
     </row>
     <row r="383">
-      <c r="A383" s="2"/>
-      <c r="B383" s="2"/>
+      <c r="A383" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="B383" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="C383" s="2"/>
       <c r="D383" s="2"/>
       <c r="E383" s="2"/>
@@ -13644,8 +13877,12 @@
       <c r="V383" s="2"/>
     </row>
     <row r="384">
-      <c r="A384" s="2"/>
-      <c r="B384" s="2"/>
+      <c r="A384" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="B384" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="C384" s="2"/>
       <c r="D384" s="2"/>
       <c r="E384" s="2"/>
@@ -13668,8 +13905,12 @@
       <c r="V384" s="2"/>
     </row>
     <row r="385">
-      <c r="A385" s="2"/>
-      <c r="B385" s="2"/>
+      <c r="A385" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="B385" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="C385" s="2"/>
       <c r="D385" s="2"/>
       <c r="E385" s="2"/>
@@ -13692,8 +13933,12 @@
       <c r="V385" s="2"/>
     </row>
     <row r="386">
-      <c r="A386" s="2"/>
-      <c r="B386" s="2"/>
+      <c r="A386" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="B386" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="C386" s="2"/>
       <c r="D386" s="2"/>
       <c r="E386" s="2"/>
@@ -13716,8 +13961,12 @@
       <c r="V386" s="2"/>
     </row>
     <row r="387">
-      <c r="A387" s="2"/>
-      <c r="B387" s="2"/>
+      <c r="A387" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="B387" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="C387" s="2"/>
       <c r="D387" s="2"/>
       <c r="E387" s="2"/>
@@ -13740,8 +13989,12 @@
       <c r="V387" s="2"/>
     </row>
     <row r="388">
-      <c r="A388" s="2"/>
-      <c r="B388" s="2"/>
+      <c r="A388" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="B388" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="C388" s="2"/>
       <c r="D388" s="2"/>
       <c r="E388" s="2"/>
@@ -13764,8 +14017,12 @@
       <c r="V388" s="2"/>
     </row>
     <row r="389">
-      <c r="A389" s="2"/>
-      <c r="B389" s="2"/>
+      <c r="A389" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="B389" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="C389" s="2"/>
       <c r="D389" s="2"/>
       <c r="E389" s="2"/>
@@ -13788,8 +14045,12 @@
       <c r="V389" s="2"/>
     </row>
     <row r="390">
-      <c r="A390" s="2"/>
-      <c r="B390" s="2"/>
+      <c r="A390" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="B390" s="5" t="s">
+        <v>618</v>
+      </c>
       <c r="C390" s="2"/>
       <c r="D390" s="2"/>
       <c r="E390" s="2"/>
@@ -13812,8 +14073,12 @@
       <c r="V390" s="2"/>
     </row>
     <row r="391">
-      <c r="A391" s="2"/>
-      <c r="B391" s="2"/>
+      <c r="A391" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="B391" s="5" t="s">
+        <v>618</v>
+      </c>
       <c r="C391" s="2"/>
       <c r="D391" s="2"/>
       <c r="E391" s="2"/>
@@ -13836,8 +14101,12 @@
       <c r="V391" s="2"/>
     </row>
     <row r="392">
-      <c r="A392" s="2"/>
-      <c r="B392" s="2"/>
+      <c r="A392" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="B392" s="5" t="s">
+        <v>618</v>
+      </c>
       <c r="C392" s="2"/>
       <c r="D392" s="2"/>
       <c r="E392" s="2"/>
@@ -13860,8 +14129,12 @@
       <c r="V392" s="2"/>
     </row>
     <row r="393">
-      <c r="A393" s="2"/>
-      <c r="B393" s="2"/>
+      <c r="A393" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="B393" s="5" t="s">
+        <v>618</v>
+      </c>
       <c r="C393" s="2"/>
       <c r="D393" s="2"/>
       <c r="E393" s="2"/>
@@ -13884,8 +14157,12 @@
       <c r="V393" s="2"/>
     </row>
     <row r="394">
-      <c r="A394" s="2"/>
-      <c r="B394" s="2"/>
+      <c r="A394" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="B394" s="5" t="s">
+        <v>618</v>
+      </c>
       <c r="C394" s="2"/>
       <c r="D394" s="2"/>
       <c r="E394" s="2"/>
